--- a/manufacturing_forms/035_steam_boiler_form--manufacturing_forms.xlsx
+++ b/manufacturing_forms/035_steam_boiler_form--manufacturing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -619,8 +619,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -648,12 +648,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'operational'}</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'operational'}</t>
+          <t>operational</t>
         </is>
       </c>
     </row>
@@ -665,12 +665,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'non_operational'}</t>
+          <t>non_operational</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'non_operational'}</t>
+          <t>non operational</t>
         </is>
       </c>
     </row>
@@ -682,12 +682,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'under_repair'}</t>
+          <t>under_repair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'under_repair'}</t>
+          <t>under repair</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
     </row>
@@ -733,12 +733,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'yearly'}</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'yearly'}</t>
+          <t>yearly</t>
         </is>
       </c>
     </row>
@@ -767,12 +767,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'passed'}</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'passed'}</t>
+          <t>passed</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'failed'}</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'failed'}</t>
+          <t>failed</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
